--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32648-2026 artfynd.xlsx
+++ b/artfynd/A 32648-2026 artfynd.xlsx
@@ -1703,7 +1703,7 @@
         <v>136095456</v>
       </c>
       <c r="B12" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>136094694</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>136094110</v>
       </c>
       <c r="B29" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
